--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -9,8 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="StampPaper" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="PakPost-Out" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Mail-In" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Mail-In" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Mail-Out" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -54,61 +54,181 @@
     <t xml:space="preserve">Link</t>
   </si>
   <si>
+    <t xml:space="preserve">eng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoteGitHub</t>
+  </si>
+  <si>
     <t xml:space="preserve">HABSM</t>
   </si>
   <si>
+    <t xml:space="preserve">The Nation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express News</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.express.com.pk/epaper/index.aspx?Issue=NP_LHE&amp;Page=Classified_PageC007&amp;Date=20260514&amp;Pageno=7&amp;View=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nation.com.pk/E-Paper/lahore/2026-05-14/page-4</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXIDE</t>
   </si>
   <si>
-    <t xml:space="preserve">The Nation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Express News</t>
+    <t xml:space="preserve">ticker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MarkInGitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAMCO does not provide registration services for ATRL, contact the relevant registrar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nishat Mills Limited has purchased RMPL and sent an offer letter to buy RMPL @Rs9,800.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATLH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHONE CALL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received phone call from Khalid of JSGlobal asking for ShareTransfer Stamps worth Rs6,000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asked to send a letter stating the needful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNERGYICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNERGY – 705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received 2+1+1 certificates for 234+233+233 shares duly transmitted in heirs’ names.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handed over to RMAK his and RMIK’s certificates with their Transferred Deeds, signed and attached copy of MIK’s cnic with both.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALEON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory Registration Details for Credit of Final Cash Dividend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiate transmission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responded with request for Member Share Holding Report from the Registrar: CDCSR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please provide Clear &amp; Visible CNIC Copy’s for Gift Deed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of, MIK, SF, RMAK, RMIK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent via PAKPOST: RGL</t>
   </si>
   <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
-    <t xml:space="preserve">ticker</t>
-  </si>
-  <si>
     <t xml:space="preserve">ref</t>
   </si>
   <si>
     <t xml:space="preserve">RGL</t>
   </si>
   <si>
-    <t xml:space="preserve">ATRL</t>
-  </si>
-  <si>
     <t xml:space="preserve">2602-2</t>
   </si>
   <si>
-    <t xml:space="preserve">RMPL</t>
+    <t xml:space="preserve">RGL166511776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit IB</t>
   </si>
   <si>
     <t xml:space="preserve">NML-RMPL – 2601</t>
   </si>
   <si>
-    <t xml:space="preserve">Ref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAMCO does not provide registration services for ATRL, contact the relevant registrar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nishat Mills Limited has purchased RMPL and sent an offer letter to buy RMPL @Rs9,800.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replied</t>
+    <t xml:space="preserve">RGL166511775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inquired ext steps for Offer Letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNERGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNERY-2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGL166511779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MARI – 2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email: gift deed attached</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HALEON – 2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGL158521956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member Share Holding Report - Late Mohammad Ayub Khan, CNIC: 35200-1521538-7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request for Member Share Holding Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSGCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARI-2602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gift Deed - Clear Copies of CNIC of deed signatories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enclosed copies of CNIC, MAK, SF, RMAK, RMIK</t>
   </si>
 </sst>
 </file>
@@ -120,7 +240,7 @@
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -141,6 +261,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -185,16 +318,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -204,6 +341,22 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -329,13 +482,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="13.69"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="11.53"/>
   </cols>
   <sheetData>
@@ -343,60 +496,84 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1600</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>46155</v>
       </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>3500</v>
+      </c>
       <c r="I2" s="2" t="n">
         <f aca="false">C2+E2+H2</f>
-        <v>1600</v>
+        <v>5100</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1600</v>
       </c>
       <c r="D3" s="1" t="n">
@@ -406,15 +583,7 @@
         <f aca="false">14.4*48</f>
         <v>691.2</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>3500</v>
-      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="2" t="n">
         <f aca="false">I2+C3+E3+H3</f>
         <v>7391.2</v>
@@ -436,50 +605,148 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="6" width="45.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="37.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="48.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>21</v>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -498,56 +765,176 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="73.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="5.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="15.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="19.4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>46156</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="0" t="s">
+        <v>46156</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>28</v>
+      <c r="C3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="StampPaper" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Mail-In" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Mail-Out" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Tasks-Transmission" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="114">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -78,6 +79,9 @@
     <t xml:space="preserve">EXIDE</t>
   </si>
   <si>
+    <t xml:space="preserve">From</t>
+  </si>
+  <si>
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
@@ -150,6 +154,9 @@
     <t xml:space="preserve">Responded with request for Member Share Holding Report from the Registrar: CDCSR</t>
   </si>
   <si>
+    <t xml:space="preserve">JSGCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARI</t>
   </si>
   <si>
@@ -162,9 +169,166 @@
     <t xml:space="preserve">Sent via PAKPOST: RGL</t>
   </si>
   <si>
+    <t xml:space="preserve">UPFL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPFL: Intimation of Book Closure Notice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folio Nr: 49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no action required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAMCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMPL-3553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMPL – Transmission case of Late Mohammad Ayub Khan against folio No. 567</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Transfer receipts: 
+MIK, 2600000776, 15-05-2026, 28
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">RMAK, 2600000777, 15-05-2026, 27
+RMIK, 2600000778, 15-05-2026, 27
+Received 2 share certificates representing 55 shares
+17014,6136468-6136517,50
+17215,6136518-6136522,5
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact CDC-SR and inform of possession of 55 shares of Rafhan Best Foods Limited. Now Unilever Foods Limited (UFL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PF-6734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packages Limited Transmission case of Late Mohammad Ayub Khan against Folio Nr. 4294</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Transfer receipts:
+MIK, 2600002340, 04-05-2026, 184
+RMAK, 2600002341, 04-05-2026, 183
+RMIK, 2600002342, 04-05-2026, 183
+Received 0 share certificates.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Wait till 22-May-2026 to receive the physical Share Certificates (with system generated Transfer Deed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbott-8070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbott Laboratories (Pakistan) Limited, Transmission case of Late Mohammad Ayub Khan against Folio Nr. 2715</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Received.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Transfer receipts:
+MIK, 2600001882, 04-05-2026, 423
+RMAK, 2600001883, 04-05-2026, 423
+RMIK, 2600001884, 04-05-2026, 423
+Received 0 share certificates.
+That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">WAFI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAFI-18161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAFI Energy Pakisgtan Limited (Formerly: Shell Pakistan Limited), Transmission case of Late Mohammad Ayub Khan against Folio Nr. KHAN0309</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Received. 
+Transfer receipts: 
+MIK, 2600007084, 04-05-2026, 590 
+RMAK, 2600007085, 04-05-2026, 589 
+RMIK, 2600007086, 04-05-2026, 589 
+Received 0 share certificates. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
+    <t xml:space="preserve">To</t>
+  </si>
+  <si>
     <t xml:space="preserve">ref</t>
   </si>
   <si>
@@ -219,16 +383,104 @@
     <t xml:space="preserve">Request for Member Share Holding Certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">JSGCL</t>
-  </si>
-  <si>
     <t xml:space="preserve">MARI-2602</t>
   </si>
   <si>
+    <t xml:space="preserve">RGL158521964</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gift Deed - Clear Copies of CNIC of deed signatories</t>
   </si>
   <si>
     <t xml:space="preserve">enclosed copies of CNIC, MAK, SF, RMAK, RMIK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re: Please provide Clear &amp; Visible CNIC Copy's for Gift Deed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mr. Khalid Pervez: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">khalid.pervez@js.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, via PAKPOST dispatched</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBF-2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGL158521970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission of Shares and Dividends – Late Mohammad Ayub Khan, CNIC: 35200-1521538-7
+    1. Rafhan Best Foods Limited (RBF)- Folio # 567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That in possession of RBF (55) shares, duly transferred in legal heirs’ names; advise next steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">userID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requestID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rDateRequested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currentStateID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilyas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiate Transmission</t>
   </si>
 </sst>
 </file>
@@ -240,7 +492,7 @@
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -264,6 +516,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -272,6 +529,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -318,7 +582,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -343,20 +607,32 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -605,148 +881,280 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="6" width="45.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="37.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="45.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="37.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="9" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="H1" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
         <v>46155</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="G2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
         <v>46155</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="G3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
         <v>46156</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="6" t="n">
         <v>46156</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="G5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
         <v>46158</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="G6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
         <v>46160</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="8" t="s">
         <v>45</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="94.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="117.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -765,176 +1173,314 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="17.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="5.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="15.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="33.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="19.4"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="5.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="15.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="19.4"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="9" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="A1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
+      <c r="H1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="6" t="n">
         <v>46156</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="C2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="F2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
         <v>46156</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="F3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="F4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="F6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
         <v>46163</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="C7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="F7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
         <v>46163</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>1</v>
+      <c r="B8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H8" r:id="rId1" display="khalid.pervez@js.com"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.69"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -190,30 +190,14 @@
     <t xml:space="preserve">RMPL – Transmission case of Late Mohammad Ayub Khan against folio No. 567</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Transfer receipts: 
+    <t xml:space="preserve">Transfer receipts: 
 MIK, 2600000776, 15-05-2026, 28
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">RMAK, 2600000777, 15-05-2026, 27
+RMAK, 2600000777, 15-05-2026, 27
 RMIK, 2600000778, 15-05-2026, 27
 Received 2 share certificates representing 55 shares
 17014,6136468-6136517,50
 17215,6136518-6136522,5
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Contact CDC-SR and inform of possession of 55 shares of Rafhan Best Foods Limited. Now Unilever Foods Limited (UFL)</t>
@@ -228,28 +212,12 @@
     <t xml:space="preserve">Packages Limited Transmission case of Late Mohammad Ayub Khan against Folio Nr. 4294</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Transfer receipts:
+    <t xml:space="preserve">Transfer receipts:
 MIK, 2600002340, 04-05-2026, 184
 RMAK, 2600002341, 04-05-2026, 183
 RMIK, 2600002342, 04-05-2026, 183
 Received 0 share certificates.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
-    </r>
+That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
   </si>
   <si>
     <t xml:space="preserve">Wait till 22-May-2026 to receive the physical Share Certificates (with system generated Transfer Deed)</t>
@@ -264,29 +232,13 @@
     <t xml:space="preserve">Abbott Laboratories (Pakistan) Limited, Transmission case of Late Mohammad Ayub Khan against Folio Nr. 2715</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Received.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Transfer receipts:
+    <t xml:space="preserve">Received.
+Transfer receipts:
 MIK, 2600001882, 04-05-2026, 423
 RMAK, 2600001883, 04-05-2026, 423
 RMIK, 2600001884, 04-05-2026, 423
 Received 0 share certificates.
 That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">WAFI</t>
@@ -298,29 +250,76 @@
     <t xml:space="preserve">WAFI Energy Pakisgtan Limited (Formerly: Shell Pakistan Limited), Transmission case of Late Mohammad Ayub Khan against Folio Nr. KHAN0309</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Received. 
+    <t xml:space="preserve">Received. 
 Transfer receipts: 
 MIK, 2600007084, 04-05-2026, 590 
 RMAK, 2600007085, 04-05-2026, 589 
 RMIK, 2600007086, 04-05-2026, 589 
 Received 0 share certificates. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
-    </r>
+That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAFI-18180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received.
+10+8+12 Total (30) certificates for 590+589+589=1,768 shares duly transmitted in the names of the legal heirs. Details:
+S0001463, MIK, 10, 590
+S0001464, RMAK, 8, 589
+S0001465, RMIK, 12, 589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledge receipt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPL-56738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pakistan Petroleum Limited, Transmission case of Late Mohammad Ayub Khan against Folio Nr. X000561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received.
+4+4+5 Total (13) certificates for 661+660+660=1,981 shares duly transmitted in the names of the legal heirs. Details:
+2600060801, X004148, MIK, 4, 661
+2600060802, X004149, RMAK, 4, 660
+2600060803, X004150, RMIK, 5, 660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PL-6751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packages Limited, Transmission case of Late Mohammad Ayub Khan against Folio Nr. 4294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received.
+7+4+9 total (20) certificates for 184+183+183=550 shares duly tranmitted in the names of the legal heirs. Details:
+8629, MIK, 7, 184
+8630, RMAK, 4, 183
+8631, RMIK,9, 183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBPL-334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reckitt Benckiser Pakistan Limited, Transmission case of Late Mohammad Ayub Khan against folio nr 2872 &amp; 4727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received. 
+Transfer receipts: 
+MIK, 2600000027, 19-05-2026, 7 
+RMAK, 2600000028, 19-05-2026, 7 
+RMIK, 2600000029, 19-05-2026, 7 
+Received 0 share certificates. 
+That: The Share Certificates will be ready within fifteen (15) days of date hereof which will be dispatched by courier to your address registered with us.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wait till 11-June-2026 to receive the physical Share Certificates (with system generated Transfer Deed)</t>
   </si>
   <si>
     <t xml:space="preserve">date</t>
@@ -401,34 +400,7 @@
     <t xml:space="preserve">Re: Please provide Clear &amp; Visible CNIC Copy's for Gift Deed</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mr. Khalid Pervez: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">khalid.pervez@js.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, via PAKPOST dispatched</t>
-    </r>
+    <t xml:space="preserve">Mr. Khalid Pervez: khalid.pervez@js.com, via PAKPOST dispatched</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-SR</t>
@@ -448,6 +420,30 @@
   </si>
   <si>
     <t xml:space="preserve">That in possession of RBF (55) shares, duly transferred in legal heirs’ names; advise next steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKGS-2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer Deed for Signature Verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKGS-2602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledgment receipt of shares </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPL-2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPL-2602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAFI-2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAFI-2602</t>
   </si>
   <si>
     <t xml:space="preserve">userID</t>
@@ -582,7 +578,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -619,8 +615,8 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -632,6 +628,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -881,7 +881,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
@@ -890,7 +890,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="14.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="45.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="37.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="7" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -919,7 +919,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>46155</v>
       </c>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="n">
         <v>46155</v>
       </c>
@@ -953,7 +953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>46156</v>
       </c>
@@ -993,7 +993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>46158</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>46160</v>
       </c>
@@ -1032,7 +1032,7 @@
       <c r="G7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       <c r="G9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       <c r="G10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       <c r="G11" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1153,8 +1153,100 @@
       <c r="G12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="9" t="n">
-        <v>1</v>
+      <c r="H12" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1173,37 +1265,37 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="6" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="5.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="15.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="33.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="19.4"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="7" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>21</v>
@@ -1223,16 +1315,16 @@
         <v>25</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>150</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>1</v>
@@ -1246,16 +1338,16 @@
         <v>28</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>1</v>
@@ -1266,19 +1358,19 @@
         <v>46157</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>1</v>
@@ -1292,13 +1384,13 @@
         <v>44</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>1</v>
@@ -1312,19 +1404,19 @@
         <v>39</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1</v>
@@ -1338,44 +1430,44 @@
         <v>43</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>46163</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1384,30 +1476,132 @@
         <v>46164</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>100</v>
+        <v>114</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>1</v>
+        <v>117</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H8" r:id="rId1" display="khalid.pervez@js.com"/>
+    <hyperlink ref="H8" r:id="rId1" display="Mr. Khalid Pervez: khalid.pervez@js.com, via PAKPOST dispatched"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1427,60 +1621,60 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="7.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="10.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="9.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="18.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="15.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="13.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>110</v>
+      <c r="A1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>113</v>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="StampPaper" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Mail-In" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Mail-Out" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Tasks-Transmission" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Tasks" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Mail-In" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Mail-Out" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Tasks-Transmission" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="163">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -77,6 +78,48 @@
   </si>
   <si>
     <t xml:space="preserve">EXIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principle Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoTicker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SubTask Step 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission of Shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engro Holdings Limited Formerly: Engro Corporation Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish newspaper ad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepare newspaper ad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get quote from publisher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receive quotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue go-ahead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick newspaper on date of publication of ad</t>
   </si>
   <si>
     <t xml:space="preserve">From</t>
@@ -322,6 +365,15 @@
     <t xml:space="preserve">Wait till 11-June-2026 to receive the physical Share Certificates (with system generated Transfer Deed)</t>
   </si>
   <si>
+    <t xml:space="preserve">CNERGY – 706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNERGYICO PK Limited, Verification of Transfer Deed (Folio Nr. 6403)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit physical shares and TD with JSGCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
@@ -425,25 +477,52 @@
     <t xml:space="preserve">PKGS-2601</t>
   </si>
   <si>
+    <t xml:space="preserve">RGL158521987</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transfer Deed for Signature Verification</t>
   </si>
   <si>
     <t xml:space="preserve">PKGS-2602</t>
   </si>
   <si>
+    <t xml:space="preserve">RGL158521988</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acknowledgment receipt of shares </t>
   </si>
   <si>
     <t xml:space="preserve">PPL-2601</t>
   </si>
   <si>
+    <t xml:space="preserve">RGL158521986</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPL-2602</t>
   </si>
   <si>
     <t xml:space="preserve">WAFI-2601</t>
   </si>
   <si>
+    <t xml:space="preserve">RGL158521985</t>
+  </si>
+  <si>
     <t xml:space="preserve">WAFI-2602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THKA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXIDE-2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGL158522012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission of =298= Shares and Unclaimed Dividends held by Late Mohammad Ayub Khan, 1. EXIDE Pakistan Limited, Folio Nr. 580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wait for response</t>
   </si>
   <si>
     <t xml:space="preserve">userID</t>
@@ -488,7 +567,7 @@
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -509,11 +588,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -578,7 +652,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -615,23 +689,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -881,372 +951,128 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="45.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="37.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="8" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="B2" s="0" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
-        <v>46155</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="D2" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="8" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
-        <v>46155</v>
-      </c>
-      <c r="C3" s="7" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="8" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="8" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
-        <v>46156</v>
-      </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="48.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>46156</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
-        <v>46158</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>46163</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="94.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>46163</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="117.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1265,7 +1091,426 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="45.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="37.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="7" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="48.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>46158</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="94.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="117.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>45069</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="6" width="11.53"/>
@@ -1273,38 +1518,38 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="5.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="15.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="33.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="19.4"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="7" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>21</v>
+        <v>105</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1312,42 +1557,42 @@
         <v>46156</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>150</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="n">
         <v>46156</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>1</v>
@@ -1358,140 +1603,140 @@
         <v>46157</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>46157</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>46163</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>101</v>
+        <v>53</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>103</v>
+        <v>119</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>46163</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>107</v>
+        <v>123</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>46163</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>111</v>
+        <v>126</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>46164</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>116</v>
+        <v>132</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>1</v>
@@ -1502,16 +1747,22 @@
         <v>46167</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>119</v>
+        <v>135</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1519,16 +1770,22 @@
         <v>46167</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>121</v>
+        <v>138</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1536,16 +1793,22 @@
         <v>46167</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>119</v>
+        <v>141</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1553,16 +1816,22 @@
         <v>46167</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>121</v>
+        <v>143</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1570,16 +1839,22 @@
         <v>46167</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>119</v>
+        <v>144</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1587,16 +1862,48 @@
         <v>46167</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>121</v>
+        <v>146</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1633,28 +1940,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1662,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="StampPaper" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="167">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -372,6 +372,18 @@
   </si>
   <si>
     <t xml:space="preserve">Submit physical shares and TD with JSGCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilever Pakistan Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intimation of Book Closure Notice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co: Unilever Pakistan Limited, Folio Nr:401, dividend Rs700 per share</t>
   </si>
   <si>
     <t xml:space="preserve">date</t>
@@ -828,7 +840,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -933,6 +945,11 @@
       <c r="I3" s="2" t="n">
         <f aca="false">I2+C3+E3+H3</f>
         <v>7391.2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>46172</v>
       </c>
     </row>
   </sheetData>
@@ -954,124 +971,124 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="20.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="3" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="36.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1091,7 +1108,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
@@ -1129,7 +1146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>46155</v>
       </c>
@@ -1146,7 +1163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="n">
         <v>46155</v>
       </c>
@@ -1163,7 +1180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>46156</v>
       </c>
@@ -1183,7 +1200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="48.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>46156</v>
       </c>
@@ -1203,7 +1220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>46158</v>
       </c>
@@ -1223,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>46160</v>
       </c>
@@ -1263,7 +1280,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="94.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>46163</v>
       </c>
@@ -1289,7 +1306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="117.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>46149</v>
       </c>
@@ -1315,7 +1332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>46149</v>
       </c>
@@ -1341,7 +1358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>46149</v>
       </c>
@@ -1367,7 +1384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>46165</v>
       </c>
@@ -1393,7 +1410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>46165</v>
       </c>
@@ -1419,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>46165</v>
       </c>
@@ -1445,7 +1462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="129.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>46165</v>
       </c>
@@ -1492,6 +1509,23 @@
       </c>
       <c r="H17" s="7" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1525,22 +1559,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>35</v>
@@ -1560,16 +1594,16 @@
         <v>39</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>150</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>1</v>
@@ -1583,16 +1617,16 @@
         <v>42</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>1</v>
@@ -1603,19 +1637,19 @@
         <v>46157</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>1</v>
@@ -1629,13 +1663,13 @@
         <v>58</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>1</v>
@@ -1649,19 +1683,19 @@
         <v>53</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>1</v>
@@ -1675,19 +1709,19 @@
         <v>57</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>1</v>
@@ -1704,13 +1738,13 @@
         <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>1</v>
@@ -1721,22 +1755,22 @@
         <v>46164</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>1</v>
@@ -1753,13 +1787,13 @@
         <v>71</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>1</v>
@@ -1776,13 +1810,13 @@
         <v>71</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>1</v>
@@ -1799,13 +1833,13 @@
         <v>87</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>1</v>
@@ -1822,13 +1856,13 @@
         <v>87</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="G13" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>1</v>
@@ -1845,13 +1879,13 @@
         <v>80</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>1</v>
@@ -1868,13 +1902,13 @@
         <v>80</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>1</v>
@@ -1885,22 +1919,22 @@
         <v>46167</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>1</v>
@@ -1940,28 +1974,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,19 +2003,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="StampPaper" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="189">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -78,6 +78,18 @@
   </si>
   <si>
     <t xml:space="preserve">EXIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nation.com.pk/E-Paper/lahore/2026-05-30/page-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.express.com.pk/epaper/index.aspx?Issue=NP_LHE&amp;Page=Classified_PageC007&amp;Date=20260530&amp;Pageno=7&amp;View=1</t>
   </si>
   <si>
     <t xml:space="preserve">Principle Task</t>
@@ -377,7 +389,10 @@
     <t xml:space="preserve">Unilever Pakistan Limited</t>
   </si>
   <si>
-    <t xml:space="preserve">UPL</t>
+    <t xml:space="preserve">ULEVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULEVER-2601</t>
   </si>
   <si>
     <t xml:space="preserve">Intimation of Book Closure Notice</t>
@@ -386,6 +401,18 @@
     <t xml:space="preserve">Co: Unilever Pakistan Limited, Folio Nr:401, dividend Rs700 per share</t>
   </si>
   <si>
+    <t xml:space="preserve">LOTCHEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3080 -LCPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notice for unclaimed dividends # D-11, D-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notice of Extraordinary General Meeting.</t>
+  </si>
+  <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
@@ -434,6 +461,9 @@
     <t xml:space="preserve">email: gift deed attached</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-SR</t>
+  </si>
+  <si>
     <t xml:space="preserve"> HALEON – 2601</t>
   </si>
   <si>
@@ -465,9 +495,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mr. Khalid Pervez: khalid.pervez@js.com, via PAKPOST dispatched</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-SR</t>
   </si>
   <si>
     <t xml:space="preserve">RBF</t>
@@ -535,6 +562,49 @@
   </si>
   <si>
     <t xml:space="preserve">wait for response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGL158522033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member Share Holding Report - Late Mohammad Ayub Khan, CNIC: 35200-1521538-7
+    1. Unilever Pakistan Limited, ULEVER, Folio #: 401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOTCHEM-2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGL158483366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission of Shares and Dividends - Late Mohammad Ayub Khan
+    1. Lotte Chemical Pakistan Limited- Folio # 61463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSCGL- KEL – 2603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 Securities submitted for Book Entry Conversion rejected
+    1. K-Electric Limited (KEL)- Folio # 17380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGROH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGROH-2602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOSS / MISSING SHARE CERTIFICATES AND TRANSMISSION OF SHARES IN THE NAME OF MOHAMMAD AYUB KHAN BE EXCHANGED WITH NEW SHARE CERTIFICATES
+    1. ENGRO HOLDINGS LIMITED (FORMERLY: DAWOOD HERCULES CORPORATION LIMITED- Folio #: KHAN0384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IB, PN with corrigendum</t>
   </si>
   <si>
     <t xml:space="preserve">userID</t>
@@ -603,6 +673,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -611,13 +688,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -664,7 +734,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -689,6 +759,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -705,15 +779,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -840,7 +914,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -951,8 +1025,79 @@
       <c r="A4" s="1" t="n">
         <v>46172</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1367</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <f aca="false">H4</f>
+        <v>1367</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1367</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <f aca="false">I4+H5</f>
+        <v>2734</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1366</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <f aca="false">I5+H6</f>
+        <v>4100</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J4" r:id="rId1" display="https://www.nation.com.pk/E-Paper/lahore/2026-05-30/page-4"/>
+    <hyperlink ref="J5" r:id="rId2" display="https://www.nation.com.pk/E-Paper/lahore/2026-05-30/page-4"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -978,118 +1123,118 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1108,424 +1253,461 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="45.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="37.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="9" width="45.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="37.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="8" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="E1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="7" t="n">
         <v>46155</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="7" t="n">
+      <c r="C2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>46155</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="7" t="n">
+      <c r="C3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>46156</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>46158</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>46156</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
-        <v>46158</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D9" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>45069</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>46163</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>46163</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D17" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
-        <v>45069</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>105</v>
+      <c r="C19" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1544,400 +1726,512 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="6" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="17.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="5.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="15.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="33.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="19.4"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="5.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="15.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="9" width="19.4"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="8" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
-        <v>46156</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="F17" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
-        <v>46156</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
-        <v>46157</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>46157</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
-        <v>46163</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
-        <v>46163</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>46163</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>1</v>
+      <c r="D18" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1974,28 +2268,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2003,19 +2297,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="192">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -605,6 +605,16 @@
   </si>
   <si>
     <t xml:space="preserve">IB, PN with corrigendum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HABSM – 2601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission of =13,775= Shares and Unclaimed Dividends held by Late Mohammad Ayub Khan
+    1. Habib Sugar Mills Limited, Folio Nr. 9840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IB, pn, eng, urdu, submitted for transmission</t>
   </si>
   <si>
     <t xml:space="preserve">userID</t>
@@ -1726,7 +1736,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="7" width="11.53"/>
@@ -2232,6 +2242,26 @@
       </c>
       <c r="H21" s="9" t="s">
         <v>177</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2268,28 +2298,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2297,19 +2327,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
